--- a/data/trans_bre/IP7_R-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP7_R-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 9,25</t>
+          <t>-2,15; 9,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 6,88</t>
+          <t>-6,33; 7,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 9,83</t>
+          <t>-5,75; 10,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 32,84</t>
+          <t>-3,05; 33,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,24 +685,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-85,87; 428,7</t>
+          <t>-89,79; 528,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-67,58; 318,94</t>
+          <t>-62,33; 302,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,74; 1273,02</t>
+          <t>-56,38; 1012,34</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 1,11</t>
+          <t>-5,86; 1,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 3,0</t>
+          <t>-5,02; 3,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 2,72</t>
+          <t>-5,2; 2,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 4,57</t>
+          <t>-2,27; 4,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 103,96</t>
+          <t>-100,0; 101,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,16; 146,21</t>
+          <t>-81,1; 186,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 297,84</t>
+          <t>-100,0; 270,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 2,33</t>
+          <t>-5,28; 2,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 4,33</t>
+          <t>-1,84; 3,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 0,0</t>
+          <t>-7,77; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,39; -0,86</t>
+          <t>-8,43; -0,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 6,73</t>
+          <t>-0,93; 7,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 6,27</t>
+          <t>-3,93; 6,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 7,95</t>
+          <t>-3,59; 8,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,65; 534,51</t>
+          <t>-83,59; 602,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 4,4</t>
+          <t>-12,35; 5,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,71; -2,82</t>
+          <t>-14,86; -2,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 6,23</t>
+          <t>-3,1; 4,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 201,02</t>
+          <t>-100,0; 289,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 2,45</t>
+          <t>-5,05; 2,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 4,04</t>
+          <t>-2,43; 4,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 2,32</t>
+          <t>-5,47; 2,34</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 2,83</t>
+          <t>-6,05; 2,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,32 +1260,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 0,65</t>
+          <t>-4,12; 1,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 2,07</t>
+          <t>-2,64; 1,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,06</t>
+          <t>-3,7; 1,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 2,07</t>
+          <t>-5,21; 2,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 224,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 426,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-92,0; 172,49</t>
+          <t>-89,02; 188,17</t>
         </is>
       </c>
     </row>
@@ -1360,32 +1360,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,88; -0,23</t>
+          <t>-5,78; 0,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,99</t>
+          <t>-1,54; 3,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,97</t>
+          <t>-1,8; 0,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,0</t>
+          <t>-1,2; 1,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-92,41; 13,41</t>
+          <t>-91,49; 29,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,52; 946,39</t>
+          <t>-71,97; 589,51</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,3; -0,54</t>
+          <t>-3,23; -0,52</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 1,22</t>
+          <t>-1,61; 1,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,02</t>
+          <t>-1,45; 0,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,64</t>
+          <t>-0,98; 3,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-74,28; -14,75</t>
+          <t>-73,33; -16,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-47,45; 72,13</t>
+          <t>-49,94; 55,18</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 70,58</t>
+          <t>-54,2; 63,75</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 201,16</t>
+          <t>-37,29; 216,36</t>
         </is>
       </c>
     </row>
